--- a/SuccessorTrace.xlsx
+++ b/SuccessorTrace.xlsx
@@ -3420,7 +3420,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>16525</v>
+        <v>19405</v>
       </c>
       <c r="B68" t="n">
         <v>25</v>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16525</v>
+        <v>19405</v>
       </c>
       <c r="B69" t="n">
         <v>26</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16527</v>
+        <v>19407</v>
       </c>
       <c r="B70" t="n">
         <v>75</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="B71" t="n">
         <v>29</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="B72" t="n">
         <v>30</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="B73" t="n">
         <v>76</v>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="B74" t="n">
         <v>77</v>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="B75" t="n">
         <v>78</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="B76" t="n">
         <v>79</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="B77" t="n">
         <v>80</v>
@@ -3852,7 +3852,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>16535</v>
+        <v>19415</v>
       </c>
       <c r="B78" t="n">
         <v>81</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>16535</v>
+        <v>19415</v>
       </c>
       <c r="B79" t="n">
         <v>82</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>16537</v>
+        <v>19417</v>
       </c>
       <c r="B80" t="n">
         <v>85</v>
@@ -3992,7 +3992,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16539</v>
+        <v>19419</v>
       </c>
       <c r="B81" t="n">
         <v>86</v>
@@ -10893,7 +10893,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>16525</v>
+        <v>19405</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -10933,10 +10933,10 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>16526</v>
+        <v>19406</v>
       </c>
       <c r="L76" t="n">
-        <v>16527</v>
+        <v>19407</v>
       </c>
       <c r="M76" t="n">
         <v>1</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>16527</v>
+        <v>19407</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -11024,10 +11024,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>16528</v>
+        <v>19408</v>
       </c>
       <c r="L77" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="M77" t="n">
         <v>1</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -11111,10 +11111,10 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>16530</v>
+        <v>19410</v>
       </c>
       <c r="L78" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
@@ -11150,7 +11150,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -11190,10 +11190,10 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>16530</v>
+        <v>19410</v>
       </c>
       <c r="L79" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="M79" t="n">
         <v>1</v>
@@ -11241,7 +11241,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -11281,10 +11281,10 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>16532</v>
+        <v>19412</v>
       </c>
       <c r="L80" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
@@ -11332,7 +11332,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -11372,10 +11372,10 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>16532</v>
+        <v>19412</v>
       </c>
       <c r="L81" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="M81" t="n">
         <v>1</v>
@@ -11419,7 +11419,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>16534</v>
+        <v>19414</v>
       </c>
       <c r="L83" t="n">
-        <v>16535</v>
+        <v>19415</v>
       </c>
       <c r="M83" t="n">
         <v>1</v>
@@ -11589,7 +11589,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>16534</v>
+        <v>19414</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>16534</v>
+        <v>19414</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>16535</v>
+        <v>19415</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -11795,10 +11795,10 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>16536</v>
+        <v>19416</v>
       </c>
       <c r="L86" t="n">
-        <v>16537</v>
+        <v>19417</v>
       </c>
       <c r="M86" t="n">
         <v>1</v>
@@ -11846,7 +11846,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>16537</v>
+        <v>19417</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>16538</v>
+        <v>19418</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>16538</v>
+        <v>19418</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46202.00069444445</v>
+        <v>46203.00069444445</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -12746,7 +12746,7 @@
         <v>483</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46202.33541666667</v>
+        <v>46203.33541666667</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -12796,7 +12796,7 @@
         <v>485</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46202.33680555555</v>
+        <v>46203.33680555555</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -12846,7 +12846,7 @@
         <v>487</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46202.33819444444</v>
+        <v>46203.33819444444</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -12896,7 +12896,7 @@
         <v>487</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46202.33819444444</v>
+        <v>46203.33819444444</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
@@ -12946,7 +12946,7 @@
         <v>489</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46202.33958333333</v>
+        <v>46203.33958333333</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
@@ -12996,7 +12996,7 @@
         <v>489</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46202.33958333333</v>
+        <v>46203.33958333333</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
@@ -13046,7 +13046,7 @@
         <v>493</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46202.34236111111</v>
+        <v>46203.34236111111</v>
       </c>
       <c r="C9" t="n">
         <v>19</v>
@@ -13096,7 +13096,7 @@
         <v>497</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46202.34513888889</v>
+        <v>46203.34513888889</v>
       </c>
       <c r="C10" t="n">
         <v>27</v>
@@ -13146,7 +13146,7 @@
         <v>620</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46202.43055555555</v>
+        <v>46203.43055555555</v>
       </c>
       <c r="C11" t="n">
         <v>23</v>
@@ -13196,7 +13196,7 @@
         <v>620</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46202.43055555555</v>
+        <v>46203.43055555555</v>
       </c>
       <c r="C12" t="n">
         <v>34</v>
@@ -13246,7 +13246,7 @@
         <v>627</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46202.43541666667</v>
+        <v>46203.43541666667</v>
       </c>
       <c r="C13" t="n">
         <v>41</v>
@@ -13296,7 +13296,7 @@
         <v>656</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46202.45555555556</v>
+        <v>46203.45555555556</v>
       </c>
       <c r="C14" t="n">
         <v>45</v>
@@ -13346,7 +13346,7 @@
         <v>744</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46202.51666666667</v>
+        <v>46203.51666666667</v>
       </c>
       <c r="C15" t="n">
         <v>48</v>
@@ -13396,7 +13396,7 @@
         <v>750</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46202.52083333334</v>
+        <v>46203.52083333334</v>
       </c>
       <c r="C16" t="n">
         <v>51</v>
@@ -13446,7 +13446,7 @@
         <v>794</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46202.55138888889</v>
+        <v>46203.55138888889</v>
       </c>
       <c r="C17" t="n">
         <v>55</v>
@@ -13496,7 +13496,7 @@
         <v>960</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46202.66666666666</v>
+        <v>46203.66666666666</v>
       </c>
       <c r="C18" t="n">
         <v>25</v>
@@ -13550,7 +13550,7 @@
         <v>960</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46202.66666666666</v>
+        <v>46203.66666666666</v>
       </c>
       <c r="C19" t="n">
         <v>29</v>
@@ -13604,7 +13604,7 @@
         <v>960</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46202.66666666666</v>
+        <v>46203.66666666666</v>
       </c>
       <c r="C20" t="n">
         <v>32</v>
@@ -13658,7 +13658,7 @@
         <v>961</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46202.66736111111</v>
+        <v>46203.66736111111</v>
       </c>
       <c r="C21" t="n">
         <v>32</v>
@@ -13712,7 +13712,7 @@
         <v>1115</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46202.77430555555</v>
+        <v>46203.77430555555</v>
       </c>
       <c r="C22" t="n">
         <v>59</v>
@@ -13762,7 +13762,7 @@
         <v>1121</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46202.77847222222</v>
+        <v>46203.77847222222</v>
       </c>
       <c r="C23" t="n">
         <v>62</v>
@@ -13812,7 +13812,7 @@
         <v>1355</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46202.94097222222</v>
+        <v>46203.94097222222</v>
       </c>
       <c r="C24" t="n">
         <v>66</v>
@@ -13862,7 +13862,7 @@
         <v>1361</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46202.94513888889</v>
+        <v>46203.94513888889</v>
       </c>
       <c r="C25" t="n">
         <v>69</v>
@@ -13912,7 +13912,7 @@
         <v>1440</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C26" t="n">
         <v>71</v>
@@ -13966,7 +13966,7 @@
         <v>1441</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46203.00069444445</v>
+        <v>46204.00069444445</v>
       </c>
       <c r="C27" t="n">
         <v>71</v>
@@ -14020,7 +14020,7 @@
         <v>1921</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46203.33402777778</v>
+        <v>46204.33402777778</v>
       </c>
       <c r="C28" t="n">
         <v>25</v>
@@ -14074,7 +14074,7 @@
         <v>1921</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46203.33402777778</v>
+        <v>46204.33402777778</v>
       </c>
       <c r="C29" t="n">
         <v>29</v>
@@ -14128,7 +14128,7 @@
         <v>2400</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46203.66666666666</v>
+        <v>46204.66666666666</v>
       </c>
       <c r="C30" t="n">
         <v>25</v>
@@ -14182,7 +14182,7 @@
         <v>2400</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46203.66666666666</v>
+        <v>46204.66666666666</v>
       </c>
       <c r="C31" t="n">
         <v>29</v>
@@ -14236,7 +14236,7 @@
         <v>3361</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46204.33402777778</v>
+        <v>46205.33402777778</v>
       </c>
       <c r="C32" t="n">
         <v>25</v>
@@ -14290,7 +14290,7 @@
         <v>3361</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46204.33402777778</v>
+        <v>46205.33402777778</v>
       </c>
       <c r="C33" t="n">
         <v>29</v>
@@ -14344,7 +14344,7 @@
         <v>3840</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46204.66666666666</v>
+        <v>46205.66666666666</v>
       </c>
       <c r="C34" t="n">
         <v>25</v>
@@ -14398,7 +14398,7 @@
         <v>3840</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46204.66666666666</v>
+        <v>46205.66666666666</v>
       </c>
       <c r="C35" t="n">
         <v>29</v>
@@ -14452,7 +14452,7 @@
         <v>4801</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46205.33402777778</v>
+        <v>46206.33402777778</v>
       </c>
       <c r="C36" t="n">
         <v>25</v>
@@ -14506,7 +14506,7 @@
         <v>4801</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46205.33402777778</v>
+        <v>46206.33402777778</v>
       </c>
       <c r="C37" t="n">
         <v>29</v>
@@ -14560,7 +14560,7 @@
         <v>5280</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46205.66666666666</v>
+        <v>46206.66666666666</v>
       </c>
       <c r="C38" t="n">
         <v>25</v>
@@ -14614,7 +14614,7 @@
         <v>5280</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46205.66666666666</v>
+        <v>46206.66666666666</v>
       </c>
       <c r="C39" t="n">
         <v>29</v>
@@ -14665,10 +14665,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6241</v>
+        <v>9121</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46206.33402777778</v>
+        <v>46209.33402777778</v>
       </c>
       <c r="C40" t="n">
         <v>25</v>
@@ -14719,10 +14719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6241</v>
+        <v>9121</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46206.33402777778</v>
+        <v>46209.33402777778</v>
       </c>
       <c r="C41" t="n">
         <v>29</v>
@@ -14773,10 +14773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6720</v>
+        <v>9600</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46206.66666666666</v>
+        <v>46209.66666666666</v>
       </c>
       <c r="C42" t="n">
         <v>25</v>
@@ -14827,10 +14827,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6720</v>
+        <v>9600</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46206.66666666666</v>
+        <v>46209.66666666666</v>
       </c>
       <c r="C43" t="n">
         <v>29</v>
@@ -14884,7 +14884,7 @@
         <v>10561</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46209.33402777778</v>
+        <v>46210.33402777778</v>
       </c>
       <c r="C44" t="n">
         <v>25</v>
@@ -14938,7 +14938,7 @@
         <v>10561</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46209.33402777778</v>
+        <v>46210.33402777778</v>
       </c>
       <c r="C45" t="n">
         <v>29</v>
@@ -14992,7 +14992,7 @@
         <v>11040</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46209.66666666666</v>
+        <v>46210.66666666666</v>
       </c>
       <c r="C46" t="n">
         <v>25</v>
@@ -15046,7 +15046,7 @@
         <v>11040</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46209.66666666666</v>
+        <v>46210.66666666666</v>
       </c>
       <c r="C47" t="n">
         <v>29</v>
@@ -15100,7 +15100,7 @@
         <v>12001</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46210.33402777778</v>
+        <v>46211.33402777778</v>
       </c>
       <c r="C48" t="n">
         <v>25</v>
@@ -15154,7 +15154,7 @@
         <v>12001</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46210.33402777778</v>
+        <v>46211.33402777778</v>
       </c>
       <c r="C49" t="n">
         <v>29</v>
@@ -15208,7 +15208,7 @@
         <v>12480</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46210.66666666666</v>
+        <v>46211.66666666666</v>
       </c>
       <c r="C50" t="n">
         <v>25</v>
@@ -15262,7 +15262,7 @@
         <v>12480</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46210.66666666666</v>
+        <v>46211.66666666666</v>
       </c>
       <c r="C51" t="n">
         <v>29</v>
@@ -15316,7 +15316,7 @@
         <v>13441</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46211.33402777778</v>
+        <v>46212.33402777778</v>
       </c>
       <c r="C52" t="n">
         <v>25</v>
@@ -15370,7 +15370,7 @@
         <v>13441</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46211.33402777778</v>
+        <v>46212.33402777778</v>
       </c>
       <c r="C53" t="n">
         <v>29</v>
@@ -15424,7 +15424,7 @@
         <v>13920</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46211.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="C54" t="n">
         <v>25</v>
@@ -15478,7 +15478,7 @@
         <v>13920</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46211.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="C55" t="n">
         <v>29</v>
@@ -15532,7 +15532,7 @@
         <v>14881</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46212.33402777778</v>
+        <v>46213.33402777778</v>
       </c>
       <c r="C56" t="n">
         <v>25</v>
@@ -15586,7 +15586,7 @@
         <v>14881</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46212.33402777778</v>
+        <v>46213.33402777778</v>
       </c>
       <c r="C57" t="n">
         <v>29</v>
@@ -15640,7 +15640,7 @@
         <v>15360</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46212.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="C58" t="n">
         <v>25</v>
@@ -15694,7 +15694,7 @@
         <v>15360</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46212.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="C59" t="n">
         <v>29</v>
@@ -15745,10 +15745,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>16321</v>
+        <v>19201</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46213.33402777778</v>
+        <v>46216.33402777778</v>
       </c>
       <c r="C60" t="n">
         <v>25</v>
@@ -15799,10 +15799,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>16321</v>
+        <v>19201</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46213.33402777778</v>
+        <v>46216.33402777778</v>
       </c>
       <c r="C61" t="n">
         <v>29</v>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>16526</v>
+        <v>19406</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46213.47638888889</v>
+        <v>46216.47638888889</v>
       </c>
       <c r="C62" t="n">
         <v>75</v>
@@ -15903,10 +15903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16530</v>
+        <v>19410</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46213.47916666666</v>
+        <v>46216.47916666666</v>
       </c>
       <c r="C63" t="n">
         <v>78</v>
@@ -15953,10 +15953,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16532</v>
+        <v>19412</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46213.48055555556</v>
+        <v>46216.48055555556</v>
       </c>
       <c r="C64" t="n">
         <v>79</v>
@@ -16003,10 +16003,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>16536</v>
+        <v>19416</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46213.48333333333</v>
+        <v>46216.48333333333</v>
       </c>
       <c r="C65" t="n">
         <v>85</v>
@@ -16053,10 +16053,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>16800</v>
+        <v>19680</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46213.66666666666</v>
+        <v>46216.66666666666</v>
       </c>
       <c r="C66" t="n">
         <v>83</v>
@@ -16107,10 +16107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16800</v>
+        <v>19680</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46213.66666666666</v>
+        <v>46216.66666666666</v>
       </c>
       <c r="C67" t="n">
         <v>87</v>
@@ -16164,7 +16164,7 @@
         <v>20641</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46216.33402777778</v>
+        <v>46217.33402777778</v>
       </c>
       <c r="C68" t="n">
         <v>83</v>
@@ -16218,7 +16218,7 @@
         <v>20641</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46216.33402777778</v>
+        <v>46217.33402777778</v>
       </c>
       <c r="C69" t="n">
         <v>87</v>
@@ -16272,7 +16272,7 @@
         <v>21120</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46216.66666666666</v>
+        <v>46217.66666666666</v>
       </c>
       <c r="C70" t="n">
         <v>83</v>
@@ -16326,7 +16326,7 @@
         <v>21120</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46216.66666666666</v>
+        <v>46217.66666666666</v>
       </c>
       <c r="C71" t="n">
         <v>87</v>
@@ -16380,7 +16380,7 @@
         <v>22081</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46217.33402777778</v>
+        <v>46218.33402777778</v>
       </c>
       <c r="C72" t="n">
         <v>83</v>
@@ -16434,7 +16434,7 @@
         <v>22081</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46217.33402777778</v>
+        <v>46218.33402777778</v>
       </c>
       <c r="C73" t="n">
         <v>87</v>
@@ -16488,7 +16488,7 @@
         <v>22560</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46217.66666666666</v>
+        <v>46218.66666666666</v>
       </c>
       <c r="C74" t="n">
         <v>83</v>
@@ -16542,7 +16542,7 @@
         <v>22560</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46217.66666666666</v>
+        <v>46218.66666666666</v>
       </c>
       <c r="C75" t="n">
         <v>87</v>
@@ -16596,7 +16596,7 @@
         <v>23521</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46218.33402777778</v>
+        <v>46219.33402777778</v>
       </c>
       <c r="C76" t="n">
         <v>83</v>
@@ -16650,7 +16650,7 @@
         <v>23521</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46218.33402777778</v>
+        <v>46219.33402777778</v>
       </c>
       <c r="C77" t="n">
         <v>87</v>
@@ -16704,7 +16704,7 @@
         <v>24000</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46218.66666666666</v>
+        <v>46219.66666666666</v>
       </c>
       <c r="C78" t="n">
         <v>83</v>
@@ -16758,7 +16758,7 @@
         <v>24000</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46218.66666666666</v>
+        <v>46219.66666666666</v>
       </c>
       <c r="C79" t="n">
         <v>87</v>
@@ -16812,7 +16812,7 @@
         <v>24961</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46219.33402777778</v>
+        <v>46220.33402777778</v>
       </c>
       <c r="C80" t="n">
         <v>83</v>
@@ -16866,7 +16866,7 @@
         <v>24961</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46219.33402777778</v>
+        <v>46220.33402777778</v>
       </c>
       <c r="C81" t="n">
         <v>87</v>
@@ -16920,7 +16920,7 @@
         <v>25440</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46219.66666666666</v>
+        <v>46220.66666666666</v>
       </c>
       <c r="C82" t="n">
         <v>83</v>
@@ -16974,7 +16974,7 @@
         <v>25440</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46219.66666666666</v>
+        <v>46220.66666666666</v>
       </c>
       <c r="C83" t="n">
         <v>87</v>
@@ -17025,10 +17025,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>26401</v>
+        <v>29281</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46220.33402777778</v>
+        <v>46223.33402777778</v>
       </c>
       <c r="C84" t="n">
         <v>83</v>
@@ -17079,10 +17079,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>26401</v>
+        <v>29281</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46220.33402777778</v>
+        <v>46223.33402777778</v>
       </c>
       <c r="C85" t="n">
         <v>87</v>
@@ -17133,10 +17133,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>26880</v>
+        <v>29760</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46220.66666666666</v>
+        <v>46223.66666666666</v>
       </c>
       <c r="C86" t="n">
         <v>83</v>
@@ -17187,10 +17187,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>26880</v>
+        <v>29760</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46220.66666666666</v>
+        <v>46223.66666666666</v>
       </c>
       <c r="C87" t="n">
         <v>87</v>
@@ -17244,7 +17244,7 @@
         <v>30721</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46223.33402777778</v>
+        <v>46224.33402777778</v>
       </c>
       <c r="C88" t="n">
         <v>83</v>
@@ -17298,7 +17298,7 @@
         <v>30721</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46223.33402777778</v>
+        <v>46224.33402777778</v>
       </c>
       <c r="C89" t="n">
         <v>87</v>
@@ -17352,7 +17352,7 @@
         <v>31200</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46223.66666666666</v>
+        <v>46224.66666666666</v>
       </c>
       <c r="C90" t="n">
         <v>83</v>
@@ -17406,7 +17406,7 @@
         <v>31200</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46223.66666666666</v>
+        <v>46224.66666666666</v>
       </c>
       <c r="C91" t="n">
         <v>87</v>
@@ -17460,7 +17460,7 @@
         <v>32161</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46224.33402777778</v>
+        <v>46225.33402777778</v>
       </c>
       <c r="C92" t="n">
         <v>83</v>
@@ -17514,7 +17514,7 @@
         <v>32161</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46224.33402777778</v>
+        <v>46225.33402777778</v>
       </c>
       <c r="C93" t="n">
         <v>87</v>
@@ -17568,7 +17568,7 @@
         <v>32640</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46224.66666666666</v>
+        <v>46225.66666666666</v>
       </c>
       <c r="C94" t="n">
         <v>83</v>
@@ -17622,7 +17622,7 @@
         <v>32640</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46224.66666666666</v>
+        <v>46225.66666666666</v>
       </c>
       <c r="C95" t="n">
         <v>87</v>
@@ -17676,7 +17676,7 @@
         <v>33601</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46225.33402777778</v>
+        <v>46226.33402777778</v>
       </c>
       <c r="C96" t="n">
         <v>83</v>
@@ -17730,7 +17730,7 @@
         <v>33601</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46225.33402777778</v>
+        <v>46226.33402777778</v>
       </c>
       <c r="C97" t="n">
         <v>87</v>
@@ -17784,7 +17784,7 @@
         <v>34080</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46225.66666666666</v>
+        <v>46226.66666666666</v>
       </c>
       <c r="C98" t="n">
         <v>83</v>
@@ -17838,7 +17838,7 @@
         <v>34080</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46225.66666666666</v>
+        <v>46226.66666666666</v>
       </c>
       <c r="C99" t="n">
         <v>87</v>
@@ -17892,7 +17892,7 @@
         <v>35041</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46226.33402777778</v>
+        <v>46227.33402777778</v>
       </c>
       <c r="C100" t="n">
         <v>83</v>
@@ -17946,7 +17946,7 @@
         <v>35041</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46226.33402777778</v>
+        <v>46227.33402777778</v>
       </c>
       <c r="C101" t="n">
         <v>87</v>
@@ -18000,7 +18000,7 @@
         <v>35445</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46226.61458333334</v>
+        <v>46227.61458333334</v>
       </c>
       <c r="C102" t="n">
         <v>89</v>
@@ -18050,7 +18050,7 @@
         <v>35449</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46226.61736111111</v>
+        <v>46227.61736111111</v>
       </c>
       <c r="C103" t="n">
         <v>92</v>
@@ -18839,7 +18839,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E9" t="n">
-        <v>16525</v>
+        <v>19405</v>
       </c>
       <c r="F9" t="n">
         <v>75</v>
@@ -18863,10 +18863,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>16526</v>
+        <v>19406</v>
       </c>
       <c r="L9" t="n">
-        <v>16527</v>
+        <v>19407</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -18930,7 +18930,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E10" t="n">
-        <v>16527</v>
+        <v>19407</v>
       </c>
       <c r="F10" t="n">
         <v>76</v>
@@ -18954,10 +18954,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>16528</v>
+        <v>19408</v>
       </c>
       <c r="L10" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -19017,7 +19017,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E11" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="F11" t="n">
         <v>77</v>
@@ -19041,10 +19041,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>16530</v>
+        <v>19410</v>
       </c>
       <c r="L11" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -19096,7 +19096,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E12" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="F12" t="n">
         <v>79</v>
@@ -19120,10 +19120,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>16532</v>
+        <v>19412</v>
       </c>
       <c r="L12" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -19187,7 +19187,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E13" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="F13" t="n">
         <v>81</v>
@@ -19278,7 +19278,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E14" t="n">
-        <v>16534</v>
+        <v>19414</v>
       </c>
       <c r="F14" t="n">
         <v>83</v>
@@ -19365,7 +19365,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E15" t="n">
-        <v>16534</v>
+        <v>19414</v>
       </c>
       <c r="F15" t="n">
         <v>84</v>
@@ -20306,7 +20306,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E26" t="n">
-        <v>16529</v>
+        <v>19409</v>
       </c>
       <c r="F26" t="n">
         <v>78</v>
@@ -20330,10 +20330,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>16530</v>
+        <v>19410</v>
       </c>
       <c r="L26" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
@@ -20397,7 +20397,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E27" t="n">
-        <v>16531</v>
+        <v>19411</v>
       </c>
       <c r="F27" t="n">
         <v>80</v>
@@ -20421,10 +20421,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>16532</v>
+        <v>19412</v>
       </c>
       <c r="L27" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -20484,7 +20484,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E28" t="n">
-        <v>16533</v>
+        <v>19413</v>
       </c>
       <c r="F28" t="n">
         <v>82</v>
@@ -20508,10 +20508,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>16534</v>
+        <v>19414</v>
       </c>
       <c r="L28" t="n">
-        <v>16535</v>
+        <v>19415</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
@@ -20563,7 +20563,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E29" t="n">
-        <v>16535</v>
+        <v>19415</v>
       </c>
       <c r="F29" t="n">
         <v>85</v>
@@ -20587,10 +20587,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>16536</v>
+        <v>19416</v>
       </c>
       <c r="L29" t="n">
-        <v>16537</v>
+        <v>19417</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
@@ -20654,7 +20654,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E30" t="n">
-        <v>16537</v>
+        <v>19417</v>
       </c>
       <c r="F30" t="n">
         <v>86</v>
@@ -20745,7 +20745,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E31" t="n">
-        <v>16538</v>
+        <v>19418</v>
       </c>
       <c r="F31" t="n">
         <v>87</v>
@@ -20832,7 +20832,7 @@
         <v>46062.04166666666</v>
       </c>
       <c r="E32" t="n">
-        <v>16538</v>
+        <v>19418</v>
       </c>
       <c r="F32" t="n">
         <v>88</v>
